--- a/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>CQP</t>
   </si>
@@ -656,171 +656,207 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F7" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="E7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="G7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="H7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="I7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="J7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="K7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="L7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="M7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>9664000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>17206000</v>
+      </c>
+      <c r="F8" s="3">
+        <v>9434000</v>
+      </c>
+      <c r="G8" s="3">
         <v>6167000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="H8" s="3">
         <v>6838000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="I8" s="3">
         <v>6426000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="J8" s="3">
         <v>4304000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="K8" s="3">
         <v>1100200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="L8" s="3">
         <v>270000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="M8" s="3">
         <v>268700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="N8" s="3">
         <v>268200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="O8" s="3">
         <v>264500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="P8" s="3">
         <v>283900</v>
       </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>3850000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>13095000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>6214000</v>
+      </c>
+      <c r="G9" s="3">
         <v>3376000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="H9" s="3">
         <v>4222000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="I9" s="3">
         <v>3829000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="J9" s="3">
         <v>2712000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="K9" s="3">
         <v>590900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="L9" s="3">
         <v>60300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="M9" s="3">
         <v>83900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="N9" s="3">
         <v>88600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="O9" s="3">
         <v>54800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="P9" s="3">
         <v>36400</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>5814000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>4111000</v>
+      </c>
+      <c r="F10" s="3">
+        <v>3220000</v>
+      </c>
+      <c r="G10" s="3">
         <v>2791000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="H10" s="3">
         <v>2616000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="I10" s="3">
         <v>2597000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="J10" s="3">
         <v>1592000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="K10" s="3">
         <v>509300</v>
-      </c>
-      <c r="I10" s="3">
-        <v>209700</v>
-      </c>
-      <c r="J10" s="3">
-        <v>184800</v>
-      </c>
-      <c r="K10" s="3">
-        <v>179600</v>
       </c>
       <c r="L10" s="3">
         <v>209700</v>
       </c>
       <c r="M10" s="3">
+        <v>184800</v>
+      </c>
+      <c r="N10" s="3">
+        <v>179600</v>
+      </c>
+      <c r="O10" s="3">
+        <v>209700</v>
+      </c>
+      <c r="P10" s="3">
         <v>247500</v>
       </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -835,8 +871,11 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -847,32 +886,41 @@
         <v>17</v>
       </c>
       <c r="F12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="3">
         <v>2000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="J12" s="3">
         <v>3000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="K12" s="3">
         <v>500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="M12" s="3">
         <v>10500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="N12" s="3">
         <v>12700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="O12" s="3">
         <v>40200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="P12" s="3">
         <v>36500</v>
       </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -906,81 +954,108 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>33000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>111000</v>
+      </c>
+      <c r="G14" s="3">
         <v>48000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="H14" s="3">
         <v>20000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="I14" s="3">
         <v>20000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="J14" s="3">
         <v>67000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="K14" s="3">
         <v>71800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="L14" s="3">
         <v>96300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="M14" s="3">
         <v>114300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="N14" s="3">
         <v>131600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="O14" s="3">
         <v>42600</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>634000</v>
+      </c>
+      <c r="F15" s="3">
+        <v>557000</v>
+      </c>
+      <c r="G15" s="3">
         <v>551000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="H15" s="3">
         <v>527000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="I15" s="3">
         <v>424000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="J15" s="3">
         <v>339000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="K15" s="3">
         <v>155600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="L15" s="3">
         <v>65700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="M15" s="3">
         <v>58600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="N15" s="3">
         <v>57500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="O15" s="3">
         <v>57800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="P15" s="3">
         <v>57900</v>
       </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -992,80 +1067,101 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>4634000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>13859000</v>
+      </c>
+      <c r="F17" s="3">
+        <v>6977000</v>
+      </c>
+      <c r="G17" s="3">
         <v>4085000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="H17" s="3">
         <v>4811000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="I17" s="3">
         <v>4459000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="J17" s="3">
         <v>3215000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="K17" s="3">
         <v>921600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="L17" s="3">
         <v>363300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="M17" s="3">
         <v>382500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="N17" s="3">
         <v>431800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="O17" s="3">
         <v>268800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="P17" s="3">
         <v>161800</v>
       </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>5030000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>3347000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>2457000</v>
+      </c>
+      <c r="G18" s="3">
         <v>2082000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="H18" s="3">
         <v>2027000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="I18" s="3">
         <v>1967000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="J18" s="3">
         <v>1089000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="K18" s="3">
         <v>178600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="L18" s="3">
         <v>-93200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="M18" s="3">
         <v>-113800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="N18" s="3">
         <v>-163600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="O18" s="3">
         <v>-4300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="P18" s="3">
         <v>122100</v>
       </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1080,152 +1176,191 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>47000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>21000</v>
+      </c>
+      <c r="F20" s="3">
+        <v>5000</v>
+      </c>
+      <c r="G20" s="3">
         <v>10000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="H20" s="3">
         <v>33000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="I20" s="3">
         <v>40000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="J20" s="3">
         <v>15000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="K20" s="3">
         <v>7100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="L20" s="3">
         <v>-225700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="M20" s="3">
         <v>-296200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="N20" s="3">
         <v>-94500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="O20" s="3">
         <v>-171100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="P20" s="3">
         <v>-175600</v>
       </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>5749000</v>
+      </c>
+      <c r="E21" s="3">
+        <v>4002000</v>
+      </c>
+      <c r="F21" s="3">
+        <v>3019000</v>
+      </c>
+      <c r="G21" s="3">
         <v>2643000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="H21" s="3">
         <v>2587000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="I21" s="3">
         <v>2431000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="J21" s="3">
         <v>1443000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="K21" s="3">
         <v>341300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="L21" s="3">
         <v>-253200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="M21" s="3">
         <v>-351400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="N21" s="3">
         <v>-200600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="O21" s="3">
         <v>-117900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="P21" s="3">
         <v>4300</v>
       </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>823000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>870000</v>
+      </c>
+      <c r="F22" s="3">
+        <v>831000</v>
+      </c>
+      <c r="G22" s="3">
         <v>909000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="H22" s="3">
         <v>885000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="I22" s="3">
         <v>733000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="J22" s="3">
         <v>614000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="K22" s="3">
         <v>356900</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="L22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M22" s="3">
-        <v>0</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="M22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4254000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>2498000</v>
+      </c>
+      <c r="F23" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="G23" s="3">
         <v>1183000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="H23" s="3">
         <v>1175000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="I23" s="3">
         <v>1274000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="J23" s="3">
         <v>490000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="K23" s="3">
         <v>-171200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="L23" s="3">
         <v>-318900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="M23" s="3">
         <v>-410000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="N23" s="3">
         <v>-258100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="O23" s="3">
         <v>-175400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="P23" s="3">
         <v>-53600</v>
       </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1259,9 +1394,18 @@
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
+        <v>0</v>
+      </c>
+      <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1295,81 +1439,108 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4254000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>2498000</v>
+      </c>
+      <c r="F26" s="3">
+        <v>1631000</v>
+      </c>
+      <c r="G26" s="3">
         <v>1183000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="H26" s="3">
         <v>1175000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="I26" s="3">
         <v>1274000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="J26" s="3">
         <v>490000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="K26" s="3">
         <v>-171200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="L26" s="3">
         <v>-318900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="M26" s="3">
         <v>-410000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="N26" s="3">
         <v>-258100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="O26" s="3">
         <v>-175400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="P26" s="3">
         <v>-53600</v>
       </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="F27" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="G27" s="3">
         <v>1066000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="H27" s="3">
         <v>1089000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="I27" s="3">
         <v>1214000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="J27" s="3">
         <v>479000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="K27" s="3">
         <v>-167800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="L27" s="3">
         <v>-312500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="M27" s="3">
         <v>-401800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="N27" s="3">
         <v>-234800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="O27" s="3">
         <v>-168500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="P27" s="3">
         <v>-52500</v>
       </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1403,9 +1574,18 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-      <c r="N28" s="3"/>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1439,9 +1619,18 @@
       <c r="M29" s="3">
         <v>0</v>
       </c>
-      <c r="N29" s="3"/>
-    </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1475,9 +1664,18 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-      <c r="N30" s="3"/>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1511,81 +1709,108 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-      <c r="N31" s="3"/>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-47000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-21000</v>
+      </c>
+      <c r="F32" s="3">
+        <v>-5000</v>
+      </c>
+      <c r="G32" s="3">
         <v>-10000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="H32" s="3">
         <v>-33000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="I32" s="3">
         <v>-40000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="J32" s="3">
         <v>-15000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="K32" s="3">
         <v>-7100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="L32" s="3">
         <v>225700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="M32" s="3">
         <v>296200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="N32" s="3">
         <v>94500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="O32" s="3">
         <v>171100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="P32" s="3">
         <v>175600</v>
       </c>
-      <c r="N32" s="3"/>
-    </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="F33" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="G33" s="3">
         <v>1066000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="H33" s="3">
         <v>1089000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="I33" s="3">
         <v>1214000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="J33" s="3">
         <v>479000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="K33" s="3">
         <v>-167800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="L33" s="3">
         <v>-312500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="M33" s="3">
         <v>-401800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="N33" s="3">
         <v>-234800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="O33" s="3">
         <v>-168500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="P33" s="3">
         <v>-52500</v>
       </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1619,86 +1844,113 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="F35" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="G35" s="3">
         <v>1066000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="H35" s="3">
         <v>1089000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="I35" s="3">
         <v>1214000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="J35" s="3">
         <v>479000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="K35" s="3">
         <v>-167800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="L35" s="3">
         <v>-312500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="M35" s="3">
         <v>-401800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="N35" s="3">
         <v>-234800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="O35" s="3">
         <v>-168500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="P35" s="3">
         <v>-52500</v>
       </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F38" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="E38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="G38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="H38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="I38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="J38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="K38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="L38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="M38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="N38" s="2"/>
-    </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1713,8 +1965,11 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1729,44 +1984,56 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>904000</v>
+      </c>
+      <c r="F41" s="3">
+        <v>876000</v>
+      </c>
+      <c r="G41" s="3">
         <v>1210000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="H41" s="3">
         <v>1781000</v>
       </c>
-      <c r="F41" s="3">
-        <v>0</v>
-      </c>
-      <c r="G41" s="3">
-        <v>0</v>
-      </c>
-      <c r="H41" s="3">
-        <v>0</v>
-      </c>
       <c r="I41" s="3">
+        <v>0</v>
+      </c>
+      <c r="J41" s="3">
+        <v>0</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+      <c r="L41" s="3">
         <v>146200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="M41" s="3">
         <v>248800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="N41" s="3">
         <v>351000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="O41" s="3">
         <v>419300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="P41" s="3">
         <v>81400</v>
       </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1800,173 +2067,218 @@
       <c r="M42" s="3">
         <v>0</v>
       </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>735000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1355000</v>
+      </c>
+      <c r="F43" s="3">
+        <v>954000</v>
+      </c>
+      <c r="G43" s="3">
         <v>646000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="H43" s="3">
         <v>560000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="I43" s="3">
         <v>690000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="J43" s="3">
         <v>390000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="K43" s="3">
         <v>227200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="L43" s="3">
         <v>42600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="M43" s="3">
         <v>31600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="N43" s="3">
         <v>14800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="O43" s="3">
         <v>7200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="P43" s="3">
         <v>1500</v>
       </c>
-      <c r="N43" s="3"/>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>142000</v>
+      </c>
+      <c r="E44" s="3">
+        <v>160000</v>
+      </c>
+      <c r="F44" s="3">
+        <v>176000</v>
+      </c>
+      <c r="G44" s="3">
         <v>107000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="H44" s="3">
         <v>116000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="I44" s="3">
         <v>99000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="J44" s="3">
         <v>95000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="K44" s="3">
         <v>97400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="L44" s="3">
         <v>16700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="M44" s="3">
         <v>7800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="N44" s="3">
         <v>10400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="O44" s="3">
         <v>9700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="P44" s="3">
         <v>4800</v>
       </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>129000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>201000</v>
+      </c>
+      <c r="F45" s="3">
+        <v>206000</v>
+      </c>
+      <c r="G45" s="3">
         <v>172000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="H45" s="3">
         <v>250000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="I45" s="3">
         <v>1567000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="J45" s="3">
         <v>1654000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="K45" s="3">
         <v>633600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="L45" s="3">
         <v>302900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="M45" s="3">
         <v>202200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="N45" s="3">
         <v>242900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="O45" s="3">
         <v>106200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="P45" s="3">
         <v>21700</v>
       </c>
-      <c r="N45" s="3"/>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1581000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>2620000</v>
+      </c>
+      <c r="F46" s="3">
+        <v>2212000</v>
+      </c>
+      <c r="G46" s="3">
         <v>2135000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="H46" s="3">
         <v>2707000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="I46" s="3">
         <v>2356000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="J46" s="3">
         <v>2139000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="K46" s="3">
         <v>958300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="L46" s="3">
         <v>493500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="M46" s="3">
         <v>486500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="N46" s="3">
         <v>613100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="O46" s="3">
         <v>533100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="P46" s="3">
         <v>109500</v>
       </c>
-      <c r="N46" s="3"/>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>126000</v>
+      </c>
+      <c r="F47" s="3">
+        <v>138000</v>
+      </c>
+      <c r="G47" s="3">
         <v>143000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="H47" s="3">
         <v>154000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="I47" s="3">
         <v>157000</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>17</v>
       </c>
       <c r="J47" s="3" t="s">
         <v>17</v>
@@ -1977,48 +2289,66 @@
       <c r="L47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3"/>
-    </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="M47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="N47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>16293000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>16814000</v>
+      </c>
+      <c r="F48" s="3">
+        <v>16928000</v>
+      </c>
+      <c r="G48" s="3">
         <v>16822000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="H48" s="3">
         <v>16462000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="I48" s="3">
         <v>15390000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="J48" s="3">
         <v>15139000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="K48" s="3">
         <v>14158200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="L48" s="3">
         <v>11931600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="M48" s="3">
         <v>8625600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="N48" s="3">
         <v>6383900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="O48" s="3">
         <v>3219600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="P48" s="3">
         <v>1514400</v>
       </c>
-      <c r="N48" s="3"/>
-    </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2052,9 +2382,18 @@
       <c r="M49" s="3">
         <v>0</v>
       </c>
-      <c r="N49" s="3"/>
-    </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N49" s="3">
+        <v>0</v>
+      </c>
+      <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2088,9 +2427,18 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-      <c r="N50" s="3"/>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2124,45 +2472,63 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-      <c r="N51" s="3"/>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>91000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>73000</v>
+      </c>
+      <c r="F52" s="3">
+        <v>80000</v>
+      </c>
+      <c r="G52" s="3">
         <v>45000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="H52" s="3">
         <v>61000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="I52" s="3">
         <v>71000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="J52" s="3">
         <v>275000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="K52" s="3">
         <v>425900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="L52" s="3">
         <v>440100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="M52" s="3">
         <v>922600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="N52" s="3">
         <v>1526300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="O52" s="3">
         <v>513100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="P52" s="3">
         <v>113400</v>
       </c>
-      <c r="N52" s="3"/>
-    </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2196,45 +2562,63 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-      <c r="N53" s="3"/>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>18102000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>19633000</v>
+      </c>
+      <c r="F54" s="3">
+        <v>19358000</v>
+      </c>
+      <c r="G54" s="3">
         <v>19145000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="H54" s="3">
         <v>19384000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="I54" s="3">
         <v>17974000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="J54" s="3">
         <v>17553000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="K54" s="3">
         <v>15542300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="L54" s="3">
         <v>12833200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="M54" s="3">
         <v>10387500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="N54" s="3">
         <v>8516800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="O54" s="3">
         <v>4265800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="P54" s="3">
         <v>1737300</v>
       </c>
-      <c r="N54" s="3"/>
-    </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2249,8 +2633,11 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2265,49 +2652,61 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>12000</v>
+        <v>69000</v>
       </c>
       <c r="E57" s="3">
-        <v>40000</v>
+        <v>32000</v>
       </c>
       <c r="F57" s="3">
-        <v>15000</v>
+        <v>21000</v>
       </c>
       <c r="G57" s="3">
         <v>12000</v>
       </c>
       <c r="H57" s="3">
+        <v>40000</v>
+      </c>
+      <c r="I57" s="3">
+        <v>15000</v>
+      </c>
+      <c r="J57" s="3">
+        <v>12000</v>
+      </c>
+      <c r="K57" s="3">
         <v>27200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="L57" s="3">
         <v>16400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="M57" s="3">
         <v>8600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="N57" s="3">
         <v>10100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="O57" s="3">
         <v>74900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="P57" s="3">
         <v>1200</v>
       </c>
-      <c r="N57" s="3"/>
-    </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>17</v>
+      <c r="D58" s="3">
+        <v>304000</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>17</v>
@@ -2315,174 +2714,219 @@
       <c r="F58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="G58" s="3">
-        <v>0</v>
-      </c>
-      <c r="H58" s="3">
+      <c r="G58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>223500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="L58" s="3">
         <v>1673400</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
-      <c r="K58" s="3" t="s">
+      <c r="M58" s="3">
+        <v>0</v>
+      </c>
+      <c r="N58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L58" s="3" t="s">
+      <c r="O58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="N58" s="3"/>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1193000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>2389000</v>
+      </c>
+      <c r="F59" s="3">
+        <v>1324000</v>
+      </c>
+      <c r="G59" s="3">
         <v>871000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="H59" s="3">
         <v>926000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="I59" s="3">
         <v>1053000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="J59" s="3">
         <v>817000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="K59" s="3">
         <v>605000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="L59" s="3">
         <v>443400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="M59" s="3">
         <v>342700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="N59" s="3">
         <v>269300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="O59" s="3">
         <v>88500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="P59" s="3">
         <v>50600</v>
       </c>
-      <c r="N59" s="3"/>
-    </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1566000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>2421000</v>
+      </c>
+      <c r="F60" s="3">
+        <v>1345000</v>
+      </c>
+      <c r="G60" s="3">
         <v>883000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="H60" s="3">
         <v>966000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="I60" s="3">
         <v>1068000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="J60" s="3">
         <v>829000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="K60" s="3">
         <v>855700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="L60" s="3">
         <v>2063000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="M60" s="3">
         <v>214800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="N60" s="3">
         <v>265900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="O60" s="3">
         <v>155800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="P60" s="3">
         <v>51800</v>
       </c>
-      <c r="N60" s="3"/>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>15620000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>16216000</v>
+      </c>
+      <c r="F61" s="3">
+        <v>17177000</v>
+      </c>
+      <c r="G61" s="3">
         <v>17580000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="H61" s="3">
         <v>17579000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="I61" s="3">
         <v>16066000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="J61" s="3">
         <v>16046000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="K61" s="3">
         <v>14209200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="L61" s="3">
         <v>10018300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="M61" s="3">
         <v>8991300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="N61" s="3">
         <v>6576300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="O61" s="3">
         <v>2167100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="P61" s="3">
         <v>2192400</v>
       </c>
-      <c r="N61" s="3"/>
-    </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1700000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>3127000</v>
+      </c>
+      <c r="F62" s="3">
+        <v>118000</v>
+      </c>
+      <c r="G62" s="3">
         <v>143000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="H62" s="3">
         <v>124000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="I62" s="3">
         <v>40000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="J62" s="3">
         <v>39000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="K62" s="3">
         <v>34300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="L62" s="3">
         <v>38900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="M62" s="3">
         <v>51000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="N62" s="3">
         <v>34900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="O62" s="3">
         <v>62900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="P62" s="3">
         <v>38100</v>
       </c>
-      <c r="N62" s="3"/>
-    </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2516,9 +2960,18 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-      <c r="N63" s="3"/>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2552,9 +3005,18 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-      <c r="N64" s="3"/>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2588,45 +3050,63 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-      <c r="N65" s="3"/>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>18886000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>21764000</v>
+      </c>
+      <c r="F66" s="3">
+        <v>18640000</v>
+      </c>
+      <c r="G66" s="3">
         <v>18606000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="H66" s="3">
         <v>18669000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="I66" s="3">
         <v>17174000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="J66" s="3">
         <v>16914000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="K66" s="3">
         <v>15099300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="L66" s="3">
         <v>12120200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="M66" s="3">
         <v>9256800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="N66" s="3">
         <v>6877000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="O66" s="3">
         <v>2385800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="P66" s="3">
         <v>2282300</v>
       </c>
-      <c r="N66" s="3"/>
-    </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2641,8 +3121,11 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2676,9 +3159,18 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-      <c r="N68" s="3"/>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2712,45 +3204,63 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-      <c r="N69" s="3"/>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>-1822000</v>
+      </c>
+      <c r="E70" s="3">
+        <v>-1013000</v>
+      </c>
+      <c r="F70" s="3">
+        <v>-306000</v>
+      </c>
+      <c r="G70" s="3">
         <v>-175000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="H70" s="3">
         <v>-81000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="I70" s="3">
         <v>-16000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="J70" s="3">
         <v>12000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="K70" s="3">
         <v>11200</v>
       </c>
-      <c r="I70" s="3">
+      <c r="L70" s="3">
         <v>16600</v>
       </c>
-      <c r="J70" s="3">
+      <c r="M70" s="3">
         <v>24900</v>
       </c>
-      <c r="K70" s="3">
+      <c r="N70" s="3">
         <v>35100</v>
       </c>
-      <c r="L70" s="3">
+      <c r="O70" s="3">
         <v>29500</v>
       </c>
-      <c r="M70" s="3">
+      <c r="P70" s="3">
         <v>-13000</v>
       </c>
-      <c r="N70" s="3"/>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2784,9 +3294,18 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-      <c r="N71" s="3"/>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -2820,9 +3339,18 @@
       <c r="M72" s="3">
         <v>0</v>
       </c>
-      <c r="N72" s="3"/>
-    </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N72" s="3">
+        <v>0</v>
+      </c>
+      <c r="O72" s="3">
+        <v>0</v>
+      </c>
+      <c r="P72" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2856,9 +3384,18 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-      <c r="N73" s="3"/>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2892,9 +3429,18 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-      <c r="N74" s="3"/>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2928,45 +3474,63 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-      <c r="N75" s="3"/>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>-1118000</v>
+      </c>
+      <c r="F76" s="3">
+        <v>1024000</v>
+      </c>
+      <c r="G76" s="3">
         <v>714000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="H76" s="3">
         <v>796000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="I76" s="3">
         <v>816000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="J76" s="3">
         <v>627000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="K76" s="3">
         <v>431900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="L76" s="3">
         <v>696300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="M76" s="3">
         <v>1105800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="N76" s="3">
         <v>1604600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="O76" s="3">
         <v>1850500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="P76" s="3">
         <v>-532000</v>
       </c>
-      <c r="N76" s="3"/>
-    </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3000,86 +3564,113 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-      <c r="N77" s="3"/>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
+        <v>44926</v>
+      </c>
+      <c r="F80" s="2">
+        <v>44561</v>
+      </c>
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="E80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="G80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="H80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="I80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="J80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="K80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="L80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="M80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="N80" s="2"/>
-    </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>3363000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1583000</v>
+      </c>
+      <c r="F81" s="3">
+        <v>1451000</v>
+      </c>
+      <c r="G81" s="3">
         <v>1066000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="H81" s="3">
         <v>1089000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="I81" s="3">
         <v>1214000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="J81" s="3">
         <v>479000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="K81" s="3">
         <v>-167800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="L81" s="3">
         <v>-312500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="M81" s="3">
         <v>-401800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="N81" s="3">
         <v>-234800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="O81" s="3">
         <v>-168500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="P81" s="3">
         <v>-52500</v>
       </c>
-      <c r="N81" s="3"/>
-    </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3094,44 +3685,56 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>672000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>634000</v>
+      </c>
+      <c r="F83" s="3">
+        <v>557000</v>
+      </c>
+      <c r="G83" s="3">
         <v>551000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="H83" s="3">
         <v>527000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="I83" s="3">
         <v>424000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3">
         <v>339000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="K83" s="3">
         <v>155600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="L83" s="3">
         <v>65700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="M83" s="3">
         <v>58600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="N83" s="3">
         <v>57500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="O83" s="3">
         <v>57500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="P83" s="3">
         <v>57900</v>
       </c>
-      <c r="N83" s="3"/>
-    </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3165,9 +3768,18 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-      <c r="N84" s="3"/>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3201,9 +3813,18 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-      <c r="N85" s="3"/>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3237,9 +3858,18 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-      <c r="N86" s="3"/>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3273,9 +3903,18 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-      <c r="N87" s="3"/>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3309,45 +3948,63 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-      <c r="N88" s="3"/>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3109000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>4149000</v>
+      </c>
+      <c r="F89" s="3">
+        <v>2291000</v>
+      </c>
+      <c r="G89" s="3">
         <v>1751000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="H89" s="3">
         <v>1547000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="I89" s="3">
         <v>1874000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="J89" s="3">
         <v>977000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="K89" s="3">
         <v>-200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="L89" s="3">
         <v>5700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="M89" s="3">
         <v>11900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="N89" s="3">
         <v>35700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="O89" s="3">
         <v>-37700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="P89" s="3">
         <v>6800</v>
       </c>
-      <c r="N89" s="3"/>
-    </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3362,44 +4019,56 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-220000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-451000</v>
+      </c>
+      <c r="F91" s="3">
+        <v>-648000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-972000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="H91" s="3">
         <v>-1331000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="I91" s="3">
         <v>-804000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="J91" s="3">
         <v>-1290000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="K91" s="3">
         <v>-2315100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="L91" s="3">
         <v>-2912100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="M91" s="3">
         <v>-2645600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="N91" s="3">
         <v>-3120600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="O91" s="3">
         <v>-1118800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="P91" s="3">
         <v>-7400</v>
       </c>
-      <c r="N91" s="3"/>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3433,9 +4102,18 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3469,45 +4147,63 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-      <c r="N93" s="3"/>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-227000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-451000</v>
+      </c>
+      <c r="F94" s="3">
+        <v>-648000</v>
+      </c>
+      <c r="G94" s="3">
         <v>-972000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="H94" s="3">
         <v>-1332000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="I94" s="3">
         <v>-804000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="J94" s="3">
         <v>-1290000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="K94" s="3">
         <v>-2353400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="L94" s="3">
         <v>-9100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="M94" s="3">
         <v>-15100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="N94" s="3">
         <v>-328800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="O94" s="3">
         <v>-4800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="P94" s="3">
         <v>-8400</v>
       </c>
-      <c r="N94" s="3"/>
-    </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3522,44 +4218,56 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-2907000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>-2635000</v>
+      </c>
+      <c r="F96" s="3">
+        <v>-1451000</v>
+      </c>
+      <c r="G96" s="3">
         <v>-1359000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="H96" s="3">
         <v>-1260000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="I96" s="3">
         <v>-1113000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="J96" s="3">
         <v>-294000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="K96" s="3">
         <v>-99000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="L96" s="3">
         <v>-99000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="M96" s="3">
         <v>-99000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="N96" s="3">
         <v>-91400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="O96" s="3">
         <v>-57800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="P96" s="3">
         <v>-48100</v>
       </c>
-      <c r="N96" s="3"/>
-    </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3593,9 +4301,18 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-      <c r="N97" s="3"/>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3629,9 +4346,18 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-      <c r="N98" s="3"/>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3665,45 +4391,63 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-      <c r="N99" s="3"/>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3247000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-3676000</v>
+      </c>
+      <c r="F100" s="3">
+        <v>-1976000</v>
+      </c>
+      <c r="G100" s="3">
         <v>-1434000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="H100" s="3">
         <v>206000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="I100" s="3">
         <v>-1118000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="J100" s="3">
         <v>1297000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="K100" s="3">
         <v>2524200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="L100" s="3">
         <v>-99300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="M100" s="3">
         <v>-99000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="N100" s="3">
         <v>224900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="O100" s="3">
         <v>380400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="P100" s="3">
         <v>29700</v>
       </c>
-      <c r="N100" s="3"/>
-    </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -3737,43 +4481,61 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3"/>
-    </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-365000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F102" s="3">
+        <v>-333000</v>
+      </c>
+      <c r="G102" s="3">
         <v>-655000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="H102" s="3">
         <v>421000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="I102" s="3">
         <v>-48000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="J102" s="3">
         <v>984000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="K102" s="3">
         <v>170500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="L102" s="3">
         <v>-102600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="M102" s="3">
         <v>-102200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="N102" s="3">
         <v>-68300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="O102" s="3">
         <v>337900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="P102" s="3">
         <v>28100</v>
       </c>
-      <c r="N102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>CQP</t>
   </si>
@@ -783,10 +783,10 @@
         <v>3376000</v>
       </c>
       <c r="H9" s="3">
-        <v>4222000</v>
+        <v>4151000</v>
       </c>
       <c r="I9" s="3">
-        <v>3829000</v>
+        <v>3929000</v>
       </c>
       <c r="J9" s="3">
         <v>2712000</v>
@@ -828,10 +828,10 @@
         <v>2791000</v>
       </c>
       <c r="H10" s="3">
-        <v>2616000</v>
+        <v>2687000</v>
       </c>
       <c r="I10" s="3">
-        <v>2597000</v>
+        <v>2497000</v>
       </c>
       <c r="J10" s="3">
         <v>1592000</v>
@@ -885,8 +885,8 @@
       <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="3">
-        <v>1000</v>
+      <c r="F12" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G12" s="3" t="s">
         <v>17</v>
@@ -976,10 +976,10 @@
         <v>33000</v>
       </c>
       <c r="F14" s="3">
-        <v>111000</v>
+        <v>101000</v>
       </c>
       <c r="G14" s="3">
-        <v>48000</v>
+        <v>43000</v>
       </c>
       <c r="H14" s="3">
         <v>20000</v>
@@ -988,7 +988,7 @@
         <v>20000</v>
       </c>
       <c r="J14" s="3">
-        <v>67000</v>
+        <v>69000</v>
       </c>
       <c r="K14" s="3">
         <v>71800</v>
@@ -1076,25 +1076,25 @@
         <v>11</v>
       </c>
       <c r="D17" s="3">
-        <v>4634000</v>
+        <v>4628000</v>
       </c>
       <c r="E17" s="3">
-        <v>13859000</v>
+        <v>13826000</v>
       </c>
       <c r="F17" s="3">
-        <v>6977000</v>
+        <v>6877000</v>
       </c>
       <c r="G17" s="3">
-        <v>4085000</v>
+        <v>4042000</v>
       </c>
       <c r="H17" s="3">
-        <v>4811000</v>
+        <v>4791000</v>
       </c>
       <c r="I17" s="3">
-        <v>4459000</v>
+        <v>4439000</v>
       </c>
       <c r="J17" s="3">
-        <v>3215000</v>
+        <v>3146000</v>
       </c>
       <c r="K17" s="3">
         <v>921600</v>
@@ -1121,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="D18" s="3">
-        <v>5030000</v>
+        <v>5036000</v>
       </c>
       <c r="E18" s="3">
-        <v>3347000</v>
+        <v>3380000</v>
       </c>
       <c r="F18" s="3">
-        <v>2457000</v>
+        <v>2557000</v>
       </c>
       <c r="G18" s="3">
-        <v>2082000</v>
+        <v>2125000</v>
       </c>
       <c r="H18" s="3">
-        <v>2027000</v>
+        <v>2047000</v>
       </c>
       <c r="I18" s="3">
-        <v>1967000</v>
+        <v>1987000</v>
       </c>
       <c r="J18" s="3">
-        <v>1089000</v>
+        <v>1158000</v>
       </c>
       <c r="K18" s="3">
         <v>178600</v>
@@ -1185,25 +1185,25 @@
         <v>14</v>
       </c>
       <c r="D20" s="3">
-        <v>47000</v>
-      </c>
-      <c r="E20" s="3">
-        <v>21000</v>
+        <v>-1000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F20" s="3">
-        <v>5000</v>
+        <v>-4000</v>
       </c>
       <c r="G20" s="3">
-        <v>10000</v>
+        <v>-10000</v>
       </c>
       <c r="H20" s="3">
-        <v>33000</v>
+        <v>-33000</v>
       </c>
       <c r="I20" s="3">
-        <v>40000</v>
+        <v>-26000</v>
       </c>
       <c r="J20" s="3">
-        <v>15000</v>
+        <v>-11000</v>
       </c>
       <c r="K20" s="3">
         <v>7100</v>
@@ -1230,25 +1230,25 @@
         <v>15</v>
       </c>
       <c r="D21" s="3">
-        <v>5749000</v>
+        <v>5709000</v>
       </c>
       <c r="E21" s="3">
-        <v>4002000</v>
+        <v>4014000</v>
       </c>
       <c r="F21" s="3">
-        <v>3019000</v>
+        <v>3118000</v>
       </c>
       <c r="G21" s="3">
-        <v>2643000</v>
+        <v>2686000</v>
       </c>
       <c r="H21" s="3">
-        <v>2587000</v>
+        <v>2607000</v>
       </c>
       <c r="I21" s="3">
-        <v>2431000</v>
+        <v>2437000</v>
       </c>
       <c r="J21" s="3">
-        <v>1443000</v>
+        <v>1508000</v>
       </c>
       <c r="K21" s="3">
         <v>341300</v>
@@ -1290,10 +1290,10 @@
         <v>885000</v>
       </c>
       <c r="I22" s="3">
-        <v>733000</v>
+        <v>719000</v>
       </c>
       <c r="J22" s="3">
-        <v>614000</v>
+        <v>610000</v>
       </c>
       <c r="K22" s="3">
         <v>356900</v>
@@ -1326,7 +1326,7 @@
         <v>2498000</v>
       </c>
       <c r="F23" s="3">
-        <v>1631000</v>
+        <v>1630000</v>
       </c>
       <c r="G23" s="3">
         <v>1183000</v>
@@ -1364,26 +1364,26 @@
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
-      </c>
-      <c r="G24" s="3">
-        <v>0</v>
-      </c>
-      <c r="H24" s="3">
-        <v>0</v>
-      </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K24" s="3">
         <v>0</v>
@@ -1461,7 +1461,7 @@
         <v>2498000</v>
       </c>
       <c r="F26" s="3">
-        <v>1631000</v>
+        <v>1630000</v>
       </c>
       <c r="G26" s="3">
         <v>1183000</v>
@@ -1500,13 +1500,13 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>3363000</v>
+        <v>3362000</v>
       </c>
       <c r="E27" s="3">
         <v>1583000</v>
       </c>
       <c r="F27" s="3">
-        <v>1451000</v>
+        <v>1450000</v>
       </c>
       <c r="G27" s="3">
         <v>1066000</v>
@@ -1725,25 +1725,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-47000</v>
-      </c>
-      <c r="E32" s="3">
-        <v>-21000</v>
+        <v>1000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="F32" s="3">
-        <v>-5000</v>
+        <v>4000</v>
       </c>
       <c r="G32" s="3">
-        <v>-10000</v>
+        <v>10000</v>
       </c>
       <c r="H32" s="3">
-        <v>-33000</v>
+        <v>33000</v>
       </c>
       <c r="I32" s="3">
-        <v>-40000</v>
+        <v>26000</v>
       </c>
       <c r="J32" s="3">
-        <v>-15000</v>
+        <v>11000</v>
       </c>
       <c r="K32" s="3">
         <v>-7100</v>
@@ -1770,25 +1770,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>3363000</v>
+        <v>4254000</v>
       </c>
       <c r="E33" s="3">
-        <v>1583000</v>
+        <v>2498000</v>
       </c>
       <c r="F33" s="3">
-        <v>1451000</v>
+        <v>1630000</v>
       </c>
       <c r="G33" s="3">
-        <v>1066000</v>
+        <v>1183000</v>
       </c>
       <c r="H33" s="3">
-        <v>1089000</v>
+        <v>1175000</v>
       </c>
       <c r="I33" s="3">
-        <v>1214000</v>
+        <v>1274000</v>
       </c>
       <c r="J33" s="3">
-        <v>479000</v>
+        <v>490000</v>
       </c>
       <c r="K33" s="3">
         <v>-167800</v>
@@ -1860,25 +1860,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>3363000</v>
+        <v>4254000</v>
       </c>
       <c r="E35" s="3">
-        <v>1583000</v>
+        <v>2498000</v>
       </c>
       <c r="F35" s="3">
-        <v>1451000</v>
+        <v>1630000</v>
       </c>
       <c r="G35" s="3">
-        <v>1066000</v>
+        <v>1183000</v>
       </c>
       <c r="H35" s="3">
-        <v>1089000</v>
+        <v>1175000</v>
       </c>
       <c r="I35" s="3">
-        <v>1214000</v>
+        <v>1274000</v>
       </c>
       <c r="J35" s="3">
-        <v>479000</v>
+        <v>490000</v>
       </c>
       <c r="K35" s="3">
         <v>-167800</v>
@@ -2007,11 +2007,11 @@
       <c r="H41" s="3">
         <v>1781000</v>
       </c>
-      <c r="I41" s="3">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3">
-        <v>0</v>
+      <c r="I41" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K41" s="3">
         <v>0</v>
@@ -2056,7 +2056,7 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>7000</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -2083,25 +2083,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>735000</v>
+        <v>652000</v>
       </c>
       <c r="E43" s="3">
-        <v>1355000</v>
+        <v>1179000</v>
       </c>
       <c r="F43" s="3">
-        <v>954000</v>
+        <v>814000</v>
       </c>
       <c r="G43" s="3">
-        <v>646000</v>
+        <v>502000</v>
       </c>
       <c r="H43" s="3">
-        <v>560000</v>
+        <v>402000</v>
       </c>
       <c r="I43" s="3">
-        <v>690000</v>
+        <v>462000</v>
       </c>
       <c r="J43" s="3">
-        <v>390000</v>
+        <v>354000</v>
       </c>
       <c r="K43" s="3">
         <v>227200</v>
@@ -2173,25 +2173,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>129000</v>
+        <v>156000</v>
       </c>
       <c r="E45" s="3">
-        <v>201000</v>
+        <v>285000</v>
       </c>
       <c r="F45" s="3">
-        <v>206000</v>
+        <v>248000</v>
       </c>
       <c r="G45" s="3">
-        <v>172000</v>
+        <v>219000</v>
       </c>
       <c r="H45" s="3">
-        <v>250000</v>
+        <v>227000</v>
       </c>
       <c r="I45" s="3">
-        <v>1567000</v>
+        <v>254000</v>
       </c>
       <c r="J45" s="3">
-        <v>1654000</v>
+        <v>94000</v>
       </c>
       <c r="K45" s="3">
         <v>633600</v>
@@ -2262,26 +2262,26 @@
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>137000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>126000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>138000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>143000</v>
-      </c>
-      <c r="H47" s="3">
-        <v>154000</v>
-      </c>
-      <c r="I47" s="3">
-        <v>157000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>17</v>
+      <c r="D47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="3">
+        <v>14000</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>17</v>
@@ -2488,25 +2488,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>91000</v>
+        <v>212000</v>
       </c>
       <c r="E52" s="3">
-        <v>73000</v>
+        <v>191000</v>
       </c>
       <c r="F52" s="3">
-        <v>80000</v>
+        <v>206000</v>
       </c>
       <c r="G52" s="3">
-        <v>45000</v>
+        <v>171000</v>
       </c>
       <c r="H52" s="3">
-        <v>61000</v>
+        <v>200000</v>
       </c>
       <c r="I52" s="3">
-        <v>71000</v>
+        <v>215000</v>
       </c>
       <c r="J52" s="3">
-        <v>275000</v>
+        <v>223000</v>
       </c>
       <c r="K52" s="3">
         <v>425900</v>
@@ -2670,10 +2670,10 @@
         <v>21000</v>
       </c>
       <c r="G57" s="3">
-        <v>12000</v>
+        <v>63000</v>
       </c>
       <c r="H57" s="3">
-        <v>40000</v>
+        <v>84000</v>
       </c>
       <c r="I57" s="3">
         <v>15000</v>
@@ -2706,22 +2706,22 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>304000</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>17</v>
+        <v>314000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>14000</v>
+      </c>
+      <c r="F58" s="3">
+        <v>8000</v>
+      </c>
+      <c r="G58" s="3">
+        <v>7000</v>
+      </c>
+      <c r="H58" s="3">
+        <v>6000</v>
+      </c>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3">
         <v>0</v>
@@ -2751,25 +2751,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1193000</v>
+        <v>449000</v>
       </c>
       <c r="E59" s="3">
-        <v>2389000</v>
+        <v>1128000</v>
       </c>
       <c r="F59" s="3">
-        <v>1324000</v>
+        <v>340000</v>
       </c>
       <c r="G59" s="3">
-        <v>871000</v>
+        <v>220000</v>
       </c>
       <c r="H59" s="3">
-        <v>926000</v>
+        <v>300000</v>
       </c>
       <c r="I59" s="3">
-        <v>1053000</v>
+        <v>262000</v>
       </c>
       <c r="J59" s="3">
-        <v>817000</v>
+        <v>198000</v>
       </c>
       <c r="K59" s="3">
         <v>605000</v>
@@ -2841,19 +2841,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>15620000</v>
+        <v>15691000</v>
       </c>
       <c r="E61" s="3">
-        <v>16216000</v>
+        <v>16296000</v>
       </c>
       <c r="F61" s="3">
-        <v>17177000</v>
+        <v>17266000</v>
       </c>
       <c r="G61" s="3">
-        <v>17580000</v>
+        <v>17670000</v>
       </c>
       <c r="H61" s="3">
-        <v>17579000</v>
+        <v>17666000</v>
       </c>
       <c r="I61" s="3">
         <v>16066000</v>
@@ -2886,19 +2886,19 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1700000</v>
+        <v>1624000</v>
       </c>
       <c r="E62" s="3">
-        <v>3127000</v>
+        <v>3039000</v>
       </c>
       <c r="F62" s="3">
-        <v>118000</v>
+        <v>27000</v>
       </c>
       <c r="G62" s="3">
-        <v>143000</v>
+        <v>53000</v>
       </c>
       <c r="H62" s="3">
-        <v>124000</v>
+        <v>37000</v>
       </c>
       <c r="I62" s="3">
         <v>40000</v>
@@ -3220,25 +3220,25 @@
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>-1822000</v>
+        <v>0</v>
       </c>
       <c r="E70" s="3">
-        <v>-1013000</v>
+        <v>0</v>
       </c>
       <c r="F70" s="3">
-        <v>-306000</v>
+        <v>0</v>
       </c>
       <c r="G70" s="3">
-        <v>-175000</v>
+        <v>0</v>
       </c>
       <c r="H70" s="3">
-        <v>-81000</v>
+        <v>0</v>
       </c>
       <c r="I70" s="3">
-        <v>-16000</v>
+        <v>0</v>
       </c>
       <c r="J70" s="3">
-        <v>12000</v>
+        <v>0</v>
       </c>
       <c r="K70" s="3">
         <v>11200</v>
@@ -3309,26 +3309,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
-        <v>0</v>
-      </c>
-      <c r="E72" s="3">
-        <v>0</v>
-      </c>
-      <c r="F72" s="3">
-        <v>0</v>
-      </c>
-      <c r="G72" s="3">
-        <v>0</v>
-      </c>
-      <c r="H72" s="3">
-        <v>0</v>
-      </c>
-      <c r="I72" s="3">
-        <v>0</v>
-      </c>
-      <c r="J72" s="3">
-        <v>0</v>
+      <c r="D72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I72" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K72" s="3">
         <v>0</v>
@@ -3630,25 +3630,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>3363000</v>
+        <v>4254000</v>
       </c>
       <c r="E81" s="3">
-        <v>1583000</v>
+        <v>2498000</v>
       </c>
       <c r="F81" s="3">
-        <v>1451000</v>
+        <v>1630000</v>
       </c>
       <c r="G81" s="3">
-        <v>1066000</v>
+        <v>1183000</v>
       </c>
       <c r="H81" s="3">
-        <v>1089000</v>
+        <v>1175000</v>
       </c>
       <c r="I81" s="3">
-        <v>1214000</v>
+        <v>1274000</v>
       </c>
       <c r="J81" s="3">
-        <v>479000</v>
+        <v>490000</v>
       </c>
       <c r="K81" s="3">
         <v>-167800</v>
@@ -4227,25 +4227,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-2907000</v>
+        <v>2013000</v>
       </c>
       <c r="E96" s="3">
-        <v>-2635000</v>
+        <v>1878000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1451000</v>
+        <v>1287000</v>
       </c>
       <c r="G96" s="3">
-        <v>-1359000</v>
+        <v>1241000</v>
       </c>
       <c r="H96" s="3">
-        <v>-1260000</v>
+        <v>1171000</v>
       </c>
       <c r="I96" s="3">
-        <v>-1113000</v>
+        <v>1059000</v>
       </c>
       <c r="J96" s="3">
-        <v>-294000</v>
+        <v>285000</v>
       </c>
       <c r="K96" s="3">
         <v>-99000</v>
@@ -4451,26 +4451,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>CQP</t>
   </si>
@@ -656,207 +656,219 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>8704000</v>
+      </c>
+      <c r="E8" s="3">
         <v>9664000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>17206000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>9434000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>6167000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6838000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6426000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4304000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1100200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>270000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>268700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>268200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>264500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>283900</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>4628000</v>
+      </c>
+      <c r="E9" s="3">
         <v>3850000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>13095000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>6214000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>3376000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4151000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>3929000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2712000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>590900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>60300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>83900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>88600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>54800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>36400</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4076000</v>
+      </c>
+      <c r="E10" s="3">
         <v>5814000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>4111000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>3220000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>2791000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2687000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2497000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1592000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>509300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>209700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>184800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>179600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>209700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>247500</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -874,8 +886,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -894,33 +907,36 @@
       <c r="H12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="3">
         <v>2000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>10500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>12700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>40200</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>36500</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -963,99 +979,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E14" s="3">
         <v>6000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>33000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>101000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>20000</v>
       </c>
       <c r="I14" s="3">
         <v>20000</v>
       </c>
       <c r="J14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="K14" s="3">
         <v>69000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>71800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>96300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>114300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>131600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>42600</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E15" s="3">
         <v>672000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>634000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>557000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>551000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>527000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>424000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>339000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>155600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>65700</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>58600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>57500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>57800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57900</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1070,98 +1095,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>5424000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4628000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>13826000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>6877000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>4042000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4791000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4439000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3146000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>921600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>363300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>382500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>431800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>268800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>161800</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3280000</v>
+      </c>
+      <c r="E18" s="3">
         <v>5036000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>3380000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>2557000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2125000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2047000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1987000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1158000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>178600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-93200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-113800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-163600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-4300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>122100</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1179,128 +1211,135 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E20" s="3">
         <v>-1000</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F20" s="3">
+      <c r="F20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G20" s="3">
         <v>-4000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-33000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-26000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-11000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>7100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-225700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-296200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-94500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-171100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-175600</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>3960000</v>
+      </c>
+      <c r="E21" s="3">
         <v>5709000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>4014000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>3118000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>2686000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2607000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2437000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>1508000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>341300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-253200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-351400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-200600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-117900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>4300</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>800000</v>
+      </c>
+      <c r="E22" s="3">
         <v>823000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>870000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>831000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>909000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>885000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>719000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>610000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>356900</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M22" s="3" t="s">
         <v>17</v>
       </c>
@@ -1310,57 +1349,63 @@
       <c r="O22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4254000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>2498000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1630000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1183000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1175000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1274000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>490000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-171200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-318900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-410000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-258100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-175400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1385,8 +1430,8 @@
       <c r="J24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
+      <c r="K24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L24" s="3">
         <v>0</v>
@@ -1403,9 +1448,12 @@
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1448,99 +1496,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4254000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>2498000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1630000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1183000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1175000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1274000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>490000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-171200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-318900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-410000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-258100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-175400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-53600</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2060000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3362000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>1583000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1450000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1066000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1089000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1214000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>479000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-167800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-312500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-401800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-234800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-168500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1583,9 +1640,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1628,9 +1688,12 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1673,9 +1736,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1718,99 +1784,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="3">
         <v>1000</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="F32" s="3">
+      <c r="F32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="3">
         <v>4000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>33000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>26000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>11000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-7100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>225700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>296200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>94500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>171100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>175600</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4254000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2498000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1630000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1183000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1175000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1274000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>490000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-167800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-312500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-401800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-234800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-168500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1853,104 +1928,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4254000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2498000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1630000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1183000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1175000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1274000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>490000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-167800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-312500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-401800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-234800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-168500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1968,8 +2052,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1987,53 +2072,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>270000</v>
+      </c>
+      <c r="E41" s="3">
         <v>575000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>904000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>876000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1210000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1781000</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="J41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K41" s="3">
-        <v>0</v>
+      <c r="K41" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L41" s="3">
+        <v>0</v>
+      </c>
+      <c r="M41" s="3">
         <v>146200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>248800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>351000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>419300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81400</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2056,11 +2145,11 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>7000</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -2076,189 +2165,204 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>652000</v>
+        <v>545000</v>
       </c>
       <c r="E43" s="3">
+        <v>651000</v>
+      </c>
+      <c r="F43" s="3">
         <v>1179000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>814000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>502000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>402000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>462000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>354000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>227200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>42600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>31600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>14800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1500</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>151000</v>
+      </c>
+      <c r="E44" s="3">
         <v>142000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>160000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>176000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>107000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>116000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>99000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>95000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>97400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>16700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>7800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>9700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4800</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>156000</v>
+        <v>250000</v>
       </c>
       <c r="E45" s="3">
+        <v>157000</v>
+      </c>
+      <c r="F45" s="3">
         <v>285000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>248000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>219000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>227000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>254000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>94000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>633600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>302900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>202200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>242900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>106200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>21700</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1325000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1581000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2620000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2212000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2135000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2707000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2356000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2139000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>958300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>493500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>486500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>613100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>533100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>109500</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2280,12 +2384,12 @@
       <c r="I47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J47" s="3">
+      <c r="J47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47" s="3">
         <v>14000</v>
       </c>
-      <c r="K47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="L47" s="3" t="s">
         <v>17</v>
       </c>
@@ -2298,57 +2402,63 @@
       <c r="O47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="P47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15839000</v>
+      </c>
+      <c r="E48" s="3">
         <v>16293000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16814000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16928000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16822000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16462000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>15390000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15139000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>14158200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>11931600</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8625600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>6383900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>3219600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1514400</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2391,9 +2501,12 @@
       <c r="P49" s="3">
         <v>0</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3">
+        <v>0</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2436,9 +2549,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2481,54 +2597,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>212000</v>
+        <v>289000</v>
       </c>
       <c r="E52" s="3">
+        <v>228000</v>
+      </c>
+      <c r="F52" s="3">
         <v>191000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>206000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>171000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>200000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>215000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>223000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>425900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>440100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>922600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1526300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>513100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>113400</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2571,54 +2693,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17453000</v>
+      </c>
+      <c r="E54" s="3">
         <v>18102000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>19633000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19358000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19145000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19384000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>17974000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17553000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15542300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>12833200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10387500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8516800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>4265800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>1737300</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2636,8 +2764,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2655,88 +2784,92 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62000</v>
+      </c>
+      <c r="E57" s="3">
         <v>69000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>21000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>63000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>84000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>12000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>27200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>16400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>10100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>74900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1200</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E58" s="3">
         <v>314000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>14000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
         <v>0</v>
       </c>
       <c r="K58" s="3">
+        <v>0</v>
+      </c>
+      <c r="L58" s="3">
         <v>223500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1673400</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>17</v>
+      <c r="N58" s="3">
+        <v>0</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>17</v>
@@ -2744,189 +2877,204 @@
       <c r="P58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>538000</v>
+      </c>
+      <c r="E59" s="3">
         <v>449000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1128000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>340000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>220000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>300000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>262000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>198000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>605000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>443400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>342700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>269300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>88500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>50600</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1712000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1566000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2421000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1345000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>883000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>966000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1068000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>829000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>855700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2063000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>214800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>265900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>155800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>51800</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14904000</v>
+      </c>
+      <c r="E61" s="3">
         <v>15691000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>16296000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>17266000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17670000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17666000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>16066000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16046000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>14209200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10018300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>8991300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>6576300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2167100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2192400</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1337000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1624000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>3039000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>37000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>40000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>39000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>38900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>51000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>34900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>62900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>38100</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2969,9 +3117,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3014,9 +3165,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3059,54 +3213,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17962000</v>
+      </c>
+      <c r="E66" s="3">
         <v>18886000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>21764000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>18640000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18606000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18669000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>17174000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>16914000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>15099300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>12120200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>9256800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6877000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2385800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2282300</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3124,8 +3284,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3168,9 +3329,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3213,9 +3377,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3241,26 +3408,29 @@
         <v>0</v>
       </c>
       <c r="K70" s="3">
+        <v>0</v>
+      </c>
+      <c r="L70" s="3">
         <v>11200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>16600</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>24900</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>35100</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>29500</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>-13000</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3303,9 +3473,12 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3330,8 +3503,8 @@
       <c r="J72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K72" s="3">
-        <v>0</v>
+      <c r="K72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L72" s="3">
         <v>0</v>
@@ -3348,9 +3521,12 @@
       <c r="P72" s="3">
         <v>0</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3">
+        <v>0</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3393,9 +3569,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3438,9 +3617,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3483,54 +3665,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>1821000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1038000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1118000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>1024000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>714000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>796000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>816000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>627000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>431900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>696300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1105800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1604600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1850500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-532000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3573,104 +3761,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2510000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4254000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2498000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1630000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1183000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1175000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1274000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>490000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-167800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-312500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-401800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-234800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-168500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-52500</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3688,53 +3885,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E83" s="3">
         <v>672000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>634000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>557000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>551000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>527000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>424000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>339000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>155600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>65700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>58600</v>
-      </c>
-      <c r="N83" s="3">
-        <v>57500</v>
       </c>
       <c r="O83" s="3">
         <v>57500</v>
       </c>
       <c r="P83" s="3">
+        <v>57500</v>
+      </c>
+      <c r="Q83" s="3">
         <v>57900</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3777,9 +3978,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3822,9 +4026,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3867,9 +4074,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3912,9 +4122,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3957,54 +4170,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2968000</v>
+      </c>
+      <c r="E89" s="3">
         <v>3109000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4149000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2291000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1751000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1547000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1874000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>977000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>5700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>11900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>35700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6800</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4022,53 +4241,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-154000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-220000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-451000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-648000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-972000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1331000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-804000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1290000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2315100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2912100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2645600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3120600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1118800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7400</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4111,9 +4334,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4156,54 +4382,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-162000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-227000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-451000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-648000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-972000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1332000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-804000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1290000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2353400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-328800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4221,34 +4453,35 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1677000</v>
+      </c>
+      <c r="E96" s="3">
         <v>2013000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>1878000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1287000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1241000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1171000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1059000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>285000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-99000</v>
       </c>
       <c r="L96" s="3">
         <v>-99000</v>
@@ -4257,17 +4490,20 @@
         <v>-99000</v>
       </c>
       <c r="N96" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-91400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-57800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-48100</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4310,9 +4546,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4355,9 +4594,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4400,54 +4642,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-3058000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3247000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3676000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1976000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1434000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>206000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1118000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1297000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>2524200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-99300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-99000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>224900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>380400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>29700</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4472,8 +4720,8 @@
       <c r="J101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4490,52 +4738,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-252000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-365000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>22000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-333000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-655000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>421000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-48000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>984000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>170500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-102600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-102200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-68300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>337900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>28100</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/CQP_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
   <si>
     <t>CQP</t>
   </si>
@@ -656,219 +656,231 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>10758000</v>
+      </c>
+      <c r="E8" s="3">
         <v>8704000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>9664000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>17206000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>9434000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6167000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6838000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6426000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4304000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1100200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>270000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>268700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>268200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>264500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>283900</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>6254000</v>
+      </c>
+      <c r="E9" s="3">
         <v>4628000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>3850000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>13095000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>6214000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>3376000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4151000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>3929000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2712000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>590900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>60300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>83900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>88600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>54800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>36400</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>4504000</v>
+      </c>
+      <c r="E10" s="3">
         <v>4076000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>5814000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>4111000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>3220000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>2791000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2687000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>2497000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1592000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>509300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>209700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>184800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>179600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>209700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>247500</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -887,8 +899,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -910,33 +923,36 @@
       <c r="I12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="J12" s="3">
+      <c r="J12" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="3">
         <v>2000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>10500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>12700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>40200</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>36500</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -982,105 +998,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>8000</v>
+      </c>
+      <c r="E14" s="3">
         <v>3000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>33000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>101000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>20000</v>
       </c>
       <c r="J14" s="3">
         <v>20000</v>
       </c>
       <c r="K14" s="3">
+        <v>20000</v>
+      </c>
+      <c r="L14" s="3">
         <v>69000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>71800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>96300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>114300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>131600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>42600</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D15" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E15" s="3">
         <v>680000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>672000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>634000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>557000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>551000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>527000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>424000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>339000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>155600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>65700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>58600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>57500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>57800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>57900</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1096,104 +1121,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>7052000</v>
+      </c>
+      <c r="E17" s="3">
         <v>5424000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4628000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>13826000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>6877000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>4042000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>4791000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>4439000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3146000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>921600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>363300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>382500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>431800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>268800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>161800</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>3706000</v>
+      </c>
+      <c r="E18" s="3">
         <v>3280000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5036000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>3380000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>2557000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>2125000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2047000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>1987000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>1158000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>178600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-93200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-113800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-163600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>122100</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -1212,137 +1244,144 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D20" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F20" s="3">
         <v>-1000</v>
       </c>
-      <c r="F20" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G20" s="3">
+      <c r="G20" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H20" s="3">
         <v>-4000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-33000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-11000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>7100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-225700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-296200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-94500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-171100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-175600</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>4418000</v>
+      </c>
+      <c r="E21" s="3">
         <v>3960000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>5709000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>4014000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>3118000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>2686000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2607000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2437000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>1508000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>341300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-253200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-351400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-200600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-117900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>4300</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>753000</v>
+      </c>
+      <c r="E22" s="3">
         <v>800000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>823000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>870000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>831000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>909000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>885000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>719000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>610000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>356900</v>
       </c>
-      <c r="M22" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="N22" s="3" t="s">
         <v>17</v>
       </c>
@@ -1352,60 +1391,66 @@
       <c r="P22" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E23" s="3">
         <v>2510000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4254000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>2498000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1630000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1183000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1175000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>1274000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>490000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-171200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-318900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-410000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-258100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-53600</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1433,8 +1478,8 @@
       <c r="K24" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
+      <c r="L24" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M24" s="3">
         <v>0</v>
@@ -1451,9 +1496,12 @@
       <c r="Q24" s="3">
         <v>0</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3">
+        <v>0</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1499,105 +1547,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E26" s="3">
         <v>2510000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4254000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>2498000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1630000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1183000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1175000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1274000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>490000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-171200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-318900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-410000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-258100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-175400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-53600</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>2504000</v>
+      </c>
+      <c r="E27" s="3">
         <v>2060000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3362000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1583000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1450000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1066000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1089000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1214000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>479000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-167800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-312500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-401800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-234800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-52500</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1643,9 +1700,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1691,9 +1751,12 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1739,9 +1802,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1787,105 +1853,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E32" s="3">
+      <c r="D32" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="3">
         <v>1000</v>
       </c>
-      <c r="F32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G32" s="3">
+      <c r="G32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="3">
         <v>4000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>33000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>11000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-7100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>225700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>296200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>94500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>171100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>175600</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2510000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>4254000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2498000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1630000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1183000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1175000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1274000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>490000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-167800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-312500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-401800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-234800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-52500</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1931,110 +2006,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2510000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>4254000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2498000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1630000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1183000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1175000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1274000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>490000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-167800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-312500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-401800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-234800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-52500</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2053,8 +2137,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2073,56 +2158,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E41" s="3">
         <v>270000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>575000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>904000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>876000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1210000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1781000</v>
       </c>
-      <c r="J41" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="K41" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L41" s="3">
-        <v>0</v>
+      <c r="L41" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M41" s="3">
+        <v>0</v>
+      </c>
+      <c r="N41" s="3">
         <v>146200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>248800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>351000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>419300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81400</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2148,11 +2237,11 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>7000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -2168,201 +2257,216 @@
       <c r="Q42" s="3">
         <v>0</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>749000</v>
+      </c>
+      <c r="E43" s="3">
         <v>545000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>651000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1179000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>814000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>502000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>402000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>462000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>354000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>227200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>42600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>31600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>14800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>7200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1500</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>180000</v>
+      </c>
+      <c r="E44" s="3">
         <v>151000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>142000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>160000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>176000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>107000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>116000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>99000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>95000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>97400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>7800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>9700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4800</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>250000</v>
+        <v>166000</v>
       </c>
       <c r="E45" s="3">
+        <v>208000</v>
+      </c>
+      <c r="F45" s="3">
         <v>157000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>285000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>248000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>219000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>227000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>254000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>94000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>633600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>302900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>202200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>242900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>106200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>21700</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1338000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1325000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1581000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2620000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2212000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2135000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2707000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2356000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2139000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>958300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>493500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>486500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>613100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>533100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>109500</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -2387,12 +2491,12 @@
       <c r="J47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L47" s="3">
         <v>14000</v>
       </c>
-      <c r="L47" s="3" t="s">
-        <v>17</v>
-      </c>
       <c r="M47" s="3" t="s">
         <v>17</v>
       </c>
@@ -2405,60 +2509,66 @@
       <c r="P47" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>15335000</v>
+      </c>
+      <c r="E48" s="3">
         <v>15839000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>16293000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>16814000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>16928000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>16822000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>16462000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>15390000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>15139000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>14158200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>11931600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8625600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>6383900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>3219600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1514400</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2504,9 +2614,12 @@
       <c r="Q49" s="3">
         <v>0</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3">
+        <v>0</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2552,9 +2665,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2600,57 +2716,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>764000</v>
+      </c>
+      <c r="E52" s="3">
         <v>289000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>228000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>191000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>206000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>171000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>200000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>215000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>223000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>425900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>440100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>922600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1526300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>513100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>113400</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2696,57 +2818,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17437000</v>
+      </c>
+      <c r="E54" s="3">
         <v>17453000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>18102000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>19633000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>19358000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>19145000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>19384000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>17974000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>17553000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15542300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>12833200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10387500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8516800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>4265800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>1737300</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2765,8 +2893,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2785,94 +2914,98 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E57" s="3">
         <v>62000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>69000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>21000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>63000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>84000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>12000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>27200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>16400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>10100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>74900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1200</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>318000</v>
+      </c>
+      <c r="E58" s="3">
         <v>361000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>314000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>14000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6000</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
-      </c>
       <c r="K58" s="3">
         <v>0</v>
       </c>
       <c r="L58" s="3">
+        <v>0</v>
+      </c>
+      <c r="M58" s="3">
         <v>223500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1673400</v>
       </c>
-      <c r="N58" s="3">
-        <v>0</v>
-      </c>
-      <c r="O58" s="3" t="s">
-        <v>17</v>
+      <c r="O58" s="3">
+        <v>0</v>
       </c>
       <c r="P58" s="3" t="s">
         <v>17</v>
@@ -2880,201 +3013,216 @@
       <c r="Q58" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>433000</v>
+      </c>
+      <c r="E59" s="3">
         <v>538000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>449000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1128000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>340000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>220000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>300000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>262000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>198000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>605000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>443400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>342700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>269300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>88500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>50600</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1708000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1712000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1566000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2421000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1345000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>883000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>966000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1068000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>829000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>855700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2063000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>214800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>265900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>155800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>51800</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>14295000</v>
+      </c>
+      <c r="E61" s="3">
         <v>14904000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>15691000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>16296000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17266000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>17670000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>17666000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>16066000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>16046000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>14209200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>10018300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>8991300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>6576300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2167100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2192400</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1010000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1337000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1624000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>3039000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>53000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>37000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>40000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>39000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>38900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>51000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>34900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>62900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>38100</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3120,9 +3268,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3168,9 +3319,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3216,57 +3370,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>17023000</v>
+      </c>
+      <c r="E66" s="3">
         <v>17962000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>18886000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>21764000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>18640000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>18606000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>18669000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>17174000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>16914000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>15099300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>12120200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9256800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6877000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2385800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2282300</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3285,8 +3445,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3332,9 +3493,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3380,9 +3544,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3411,26 +3578,29 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
+        <v>0</v>
+      </c>
+      <c r="M70" s="3">
         <v>11200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>16600</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>24900</v>
       </c>
-      <c r="O70" s="3">
+      <c r="P70" s="3">
         <v>35100</v>
       </c>
-      <c r="P70" s="3">
+      <c r="Q70" s="3">
         <v>29500</v>
       </c>
-      <c r="Q70" s="3">
+      <c r="R70" s="3">
         <v>-13000</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3476,9 +3646,12 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -3506,8 +3679,8 @@
       <c r="K72" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L72" s="3">
-        <v>0</v>
+      <c r="L72" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M72" s="3">
         <v>0</v>
@@ -3524,9 +3697,12 @@
       <c r="Q72" s="3">
         <v>0</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3">
+        <v>0</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3572,9 +3748,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3620,9 +3799,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3668,57 +3850,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>3156000</v>
+      </c>
+      <c r="E76" s="3">
         <v>1821000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>1038000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1118000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>1024000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>714000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>796000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>816000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>627000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>431900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>696300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>1105800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>1604600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>1850500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-532000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3764,110 +3952,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2987000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2510000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>4254000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2498000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1630000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1183000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1175000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1274000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>490000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-167800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-312500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-401800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-234800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-168500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-52500</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3886,56 +4083,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>688000</v>
+      </c>
+      <c r="E83" s="3">
         <v>680000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>672000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>634000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>557000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>551000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>527000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>424000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>339000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>155600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>65700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>58600</v>
-      </c>
-      <c r="O83" s="3">
-        <v>57500</v>
       </c>
       <c r="P83" s="3">
         <v>57500</v>
       </c>
       <c r="Q83" s="3">
+        <v>57500</v>
+      </c>
+      <c r="R83" s="3">
         <v>57900</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3981,9 +4182,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4029,9 +4233,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4077,9 +4284,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4125,9 +4335,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4173,57 +4386,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2768000</v>
+      </c>
+      <c r="E89" s="3">
         <v>2968000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>3109000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>4149000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>2291000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>1751000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>1547000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1874000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>977000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>5700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>11900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>35700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6800</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4242,56 +4461,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-199000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-154000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-220000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-451000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-648000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-972000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1331000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-804000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1290000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2315100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2912100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2645600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3120600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1118800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7400</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4337,9 +4560,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4385,57 +4611,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-204000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-162000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-227000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-451000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-648000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-972000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1332000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-804000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1290000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2353400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-9100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-328800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8400</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4454,37 +4686,38 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>1592000</v>
+      </c>
+      <c r="E96" s="3">
         <v>1677000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>2013000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>1878000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>1287000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>1241000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>1171000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>1059000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>285000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-99000</v>
       </c>
       <c r="M96" s="3">
         <v>-99000</v>
@@ -4493,17 +4726,20 @@
         <v>-99000</v>
       </c>
       <c r="O96" s="3">
+        <v>-99000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-91400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-57800</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-48100</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4549,9 +4785,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4597,9 +4836,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4645,57 +4887,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-2742000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-3058000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-3247000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-3676000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1976000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1434000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>206000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1118000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1297000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>2524200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-99300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-99000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>224900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>380400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>29700</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4723,8 +4971,8 @@
       <c r="K101" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4741,55 +4989,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-178000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-252000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-365000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>22000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-333000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-655000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>421000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-48000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>984000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>170500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-102600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-102200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-68300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>337900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>28100</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
